--- a/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 12,21</t>
+          <t>-3,66; 12,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 8,01</t>
+          <t>-8,81; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 5,47</t>
+          <t>-10,04; 5,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 49,03</t>
+          <t>-9,16; 45,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 333,71</t>
+          <t>-36,46; 285,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 133,31</t>
+          <t>-60,42; 137,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,7; 217,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,23</t>
+          <t>-3,62; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,7</t>
+          <t>-4,13; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,77</t>
+          <t>-0,12; 6,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 9,8</t>
+          <t>-1,84; 9,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 35,61</t>
+          <t>-37,29; 34,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 30,75</t>
+          <t>-34,61; 27,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 102,78</t>
+          <t>-1,6; 97,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 559,24</t>
+          <t>-46,18; 457,06</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,38</t>
+          <t>-4,91; 6,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 7,6</t>
+          <t>-3,92; 7,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -0,45</t>
+          <t>-10,63; 0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 11,36</t>
+          <t>-9,25; 10,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 87,46</t>
+          <t>-40,08; 90,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 108,25</t>
+          <t>-33,79; 113,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,24; -3,61</t>
+          <t>-74,86; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,74</t>
+          <t>-2,33; 2,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,68</t>
+          <t>-2,73; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,37</t>
+          <t>-1,94; 3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,46</t>
+          <t>-1,13; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 38,7</t>
+          <t>-24,54; 38,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 31,72</t>
+          <t>-24,46; 30,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 45,02</t>
+          <t>-19,34; 47,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 420,35</t>
+          <t>-28,56; 410,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 12,59</t>
+          <t>-3,57; 11,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 8,19</t>
+          <t>-8,69; 7,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 5,53</t>
+          <t>-8,85; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 45,65</t>
+          <t>-9,13; 45,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 285,32</t>
+          <t>-37,28; 291,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 137,17</t>
+          <t>-60,17; 121,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 217,11</t>
+          <t>-85,58; 204,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,14</t>
+          <t>-3,92; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,35</t>
+          <t>-4,17; 2,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,3</t>
+          <t>0,01; 6,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 9,66</t>
+          <t>-1,6; 8,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 34,54</t>
+          <t>-41,2; 37,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 27,58</t>
+          <t>-34,88; 29,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 97,27</t>
+          <t>0,01; 99,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 457,06</t>
+          <t>-37,43; 470,6</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 6,53</t>
+          <t>-5,14; 6,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 7,16</t>
+          <t>-4,0; 7,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 0,15</t>
+          <t>-10,38; 0,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 10,0</t>
+          <t>-8,48; 11,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 90,93</t>
+          <t>-39,8; 98,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 113,66</t>
+          <t>-33,65; 109,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 3,74</t>
+          <t>-72,0; 9,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,78</t>
+          <t>-2,33; 2,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,61</t>
+          <t>-2,57; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,47</t>
+          <t>-1,99; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,21</t>
+          <t>-1,09; 8,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 38,34</t>
+          <t>-24,6; 34,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 30,5</t>
+          <t>-23,17; 32,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 47,03</t>
+          <t>-19,62; 42,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 410,84</t>
+          <t>-31,08; 390,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>178,0%</t>
+          <t>167,77%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 11,23</t>
+          <t>-3,52; 12,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,86</t>
+          <t>-8,42; 8,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 5,41</t>
+          <t>-10,12; 5,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 45,2</t>
+          <t>-8,02; 47,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 291,83</t>
+          <t>-36,09; 333,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 121,48</t>
+          <t>-54,07; 133,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 204,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>127,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,26</t>
+          <t>-3,96; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,45</t>
+          <t>-4,31; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,01; 6,57</t>
+          <t>0,2; 6,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,91</t>
+          <t>-0,99; 10,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 37,18</t>
+          <t>-41,99; 35,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 29,58</t>
+          <t>-36,24; 30,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,01; 99,86</t>
+          <t>0,58; 102,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 470,6</t>
+          <t>-38,67; 687,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,64</t>
+          <t>-5,45; 6,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,37</t>
+          <t>-4,24; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 0,01</t>
+          <t>-10,08; -0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 11,89</t>
+          <t>-9,5; 13,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 98,21</t>
+          <t>-42,4; 87,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 109,24</t>
+          <t>-34,95; 108,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 9,09</t>
+          <t>-73,24; -3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,48</t>
+          <t>-2,35; 2,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,68</t>
+          <t>-2,87; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,19</t>
+          <t>-1,71; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,81</t>
+          <t>-1,1; 9,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 34,56</t>
+          <t>-24,5; 38,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 32,45</t>
+          <t>-24,7; 31,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 42,47</t>
+          <t>-17,06; 45,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 390,59</t>
+          <t>-29,5; 457,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,07</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,84</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-25,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>167,77%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.071121360722614</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2186812541250846</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.854917467371274</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.83823388708904</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5512968959016289</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02087283269543834</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2587336503269747</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.677703255188307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 12,21</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,42; 8,01</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,12; 5,47</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,02; 47,12</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-36,09; 333,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-54,07; 133,31</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.522556513794946</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.415571648052492</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.11530633568266</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.018165970340592</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3608857308395876</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5406604732403684</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.21296571709846</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.013420881492788</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.474519994146375</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>47.12232552041321</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.337142993762299</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.333065092224974</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-8,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>127,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 2,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,31; 2,7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 6,77</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 10,43</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-41,99; 35,61</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-36,24; 30,75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 102,78</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,67; 687,07</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.855972383984957</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8894128119371236</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.170297521129793</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.928334084770225</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1064683977527669</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.08839411089361318</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3988425653987147</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.279403593706473</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-47,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.964342899479603</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.305429389518786</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1983643643079147</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.9928971895140585</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4199176439690249</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.36236158694182</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.005824313443173147</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3867335154227915</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 6,38</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 7,6</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,08; -0,45</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,5; 13,03</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-42,4; 87,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-34,95; 108,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-73,24; -3,61</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.233021086940889</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.699377571624423</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.771168660710988</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.43404584173385</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3561101219886829</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3075112852459189</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.027752313126387</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>6.870694600614415</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +811,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.6305573260289271</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.751800722133792</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.347404988898463</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.4372155372163081</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.06388910386713921</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1887870653338324</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4702958929065787</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.09079498528080183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 2,74</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 2,68</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 3,37</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 9,85</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-24,5; 38,7</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,7; 31,72</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-17,06; 45,02</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-29,5; 457,09</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.454786457386965</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.243443482409708</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.0774129699384</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.502396606450519</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.424033556316451</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3495057671786508</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7324073013806977</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.375639672416185</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.602643034283436</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.4498015626657629</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>13.03279034606552</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8745575622548236</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.082511016054615</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.03611661872252445</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1767738832844451</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1175081205073647</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6549749645332823</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.422645378771939</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02111327896375419</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01183857417035207</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07482316246469671</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.9159230222830604</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.348685492386986</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.868663518690697</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.709905473812558</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.098157685879488</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2449821885319131</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2469599229730964</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.170592426250566</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2950211345951732</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.738377361151361</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.680829567568341</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.374837299810923</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.852401927746843</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3869609070691624</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3172259428786426</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4502107027156207</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>4.570886511026245</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1005,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
